--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -85,142 +85,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>VAS</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>BRYANA</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>LUZ ELENA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ROSMELY LEILANI</t>
-  </si>
-  <si>
-    <t>ANGEL OSWALDO</t>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>IRVING JESUS</t>
   </si>
   <si>
     <t>MARTIN ERNESTO</t>
   </si>
   <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
     <t>JUAN RAMON</t>
   </si>
   <si>
-    <t>SERGIO GISELL</t>
-  </si>
-  <si>
-    <t>NAHUM OMAR</t>
-  </si>
-  <si>
-    <t>MARIA ESTELA</t>
-  </si>
-  <si>
     <t>EUNICE GUADALUPE</t>
   </si>
   <si>
-    <t>EMIRETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PAOLA MELANIE</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>EMERSON IVAN</t>
+    <t>SABDIEL JIREH</t>
   </si>
 </sst>
 </file>
@@ -621,16 +555,16 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -816,16 +750,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.5</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -839,16 +776,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>67.65000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -862,16 +802,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>69.7</v>
+      </c>
+      <c r="H4">
+        <v>5.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -885,16 +828,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>52.17</v>
+      </c>
+      <c r="H5">
+        <v>5.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -908,16 +854,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H6">
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -931,16 +880,19 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>47.62</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -993,19 +945,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>82.5</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1031,7 +983,7 @@
         <v>67.65000000000001</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1048,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>45.45</v>
+        <v>69.7</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1074,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
         <v>12</v>
       </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
       <c r="G5">
-        <v>47.83</v>
+        <v>52.17</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1100,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1135,7 +1087,7 @@
         <v>47.62</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1177,22 +1129,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920403</v>
+        <v>24330051920330</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
-        <v>50</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1200,22 +1152,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920400</v>
+        <v>24330051920256</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1223,22 +1175,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920298</v>
+        <v>24330051920270</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" t="s">
-        <v>52</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1246,22 +1198,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920244</v>
+        <v>23330051920192</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1269,22 +1221,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920396</v>
+        <v>23330051920329</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1292,22 +1244,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920265</v>
+        <v>23330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1315,277 +1267,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920266</v>
+        <v>24330051920226</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920270</v>
+        <v>24330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920201</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920090</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920302</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920076</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920226</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920408</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920230</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920231</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920245</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920289</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -91,21 +91,21 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -115,21 +115,21 @@
     <t>CAMACHO</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ROSALES</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
@@ -139,19 +139,19 @@
     <t>IRVING JESUS</t>
   </si>
   <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>JUAN RAMON</t>
+  </si>
+  <si>
+    <t>EUNICE GUADALUPE</t>
+  </si>
+  <si>
     <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
-  </si>
-  <si>
-    <t>EUNICE GUADALUPE</t>
   </si>
   <si>
     <t>SABDIEL JIREH</t>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920270</v>
+        <v>23330051920192</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1187,10 +1187,10 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920192</v>
+        <v>23330051920329</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920329</v>
+        <v>23330051920201</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920201</v>
+        <v>24330051920226</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1256,18 +1256,18 @@
         <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920226</v>
+        <v>24330051920270</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
@@ -1282,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>1</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -85,7 +85,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -103,9 +103,6 @@
     <t>LEYVA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -133,7 +130,7 @@
     <t>PERALTA</t>
   </si>
   <si>
-    <t>DANIELA LILI</t>
+    <t>ERIKA VALERIA</t>
   </si>
   <si>
     <t>IRVING JESUS</t>
@@ -1129,16 +1126,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920330</v>
+        <v>24330051920238</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,10 +1155,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1181,10 +1178,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1204,10 +1201,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1227,10 +1224,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1250,10 +1247,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1270,13 +1267,13 @@
         <v>24330051920270</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1293,13 +1290,13 @@
         <v>24330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,15 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -100,42 +109,45 @@
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>CAMACHO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>ERIKA VALERIA</t>
   </si>
   <si>
     <t>IRVING JESUS</t>
   </si>
   <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>EUNICE GUADALUPE</t>
+  </si>
+  <si>
+    <t>MARTIN ERNESTO</t>
+  </si>
+  <si>
+    <t>SABDIEL JIREH</t>
+  </si>
+  <si>
     <t>KEVYN DANIEL</t>
   </si>
   <si>
@@ -143,15 +155,6 @@
   </si>
   <si>
     <t>JUAN RAMON</t>
-  </si>
-  <si>
-    <t>EUNICE GUADALUPE</t>
-  </si>
-  <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
-    <t>SABDIEL JIREH</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,7 +1135,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -1172,7 +1175,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920192</v>
+        <v>23330051920203</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1195,7 +1198,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920329</v>
+        <v>24330051920226</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1207,21 +1210,21 @@
         <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920201</v>
+        <v>24330051920270</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -1230,21 +1233,21 @@
         <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920226</v>
+        <v>24330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
@@ -1256,7 +1259,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1264,10 +1267,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920270</v>
+        <v>23330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -1276,10 +1279,10 @@
         <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1287,7 +1290,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920323</v>
+        <v>23330051920329</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1299,12 +1302,35 @@
         <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920201</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="94">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,57 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MAZA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -109,15 +157,51 @@
     <t>MARQUEZ</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>CAMACHO</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ROSALES</t>
   </si>
   <si>
@@ -128,6 +212,66 @@
   </si>
   <si>
     <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>VICTOR YAEL</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>ALEYDA MONSERRAT</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>JHOCELIN VALENTINA</t>
+  </si>
+  <si>
+    <t>KEVIN JESUS</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>HEIDI ABRIL</t>
   </si>
   <si>
     <t>ERIKA VALERIA</t>
@@ -1097,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,208 +1273,668 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920238</v>
+        <v>24330051920092</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920256</v>
+        <v>24330051920400</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920203</v>
+        <v>24330051920194</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920226</v>
+        <v>24330051920202</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920270</v>
+        <v>24330051920239</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920323</v>
+        <v>24330051920267</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920192</v>
+        <v>24330051920369</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920329</v>
+        <v>24330051920283</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920201</v>
+        <v>23330051920312</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920183</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920189</v>
+      </c>
+      <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920195</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920202</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920098</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920355</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920179</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920298</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920330</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920390</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920262</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920238</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920256</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920203</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920226</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920270</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920323</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920192</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920329</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920201</v>
+      </c>
+      <c r="B30" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
+      <c r="C30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" t="s">
         <v>9</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F30" t="s">
         <v>15</v>
       </c>
-      <c r="G10">
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="122">
   <si>
     <t>Mat</t>
   </si>
@@ -85,69 +85,93 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ZENDEJAS</t>
-  </si>
-  <si>
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>TORRES</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MAZA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -157,37 +181,67 @@
     <t>MARQUEZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>GALLARDO</t>
+    <t>BALDERAS</t>
   </si>
   <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
     <t>BONILLA</t>
   </si>
   <si>
     <t>CHACON</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>RUL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
   </si>
   <si>
     <t>ENCARNACION</t>
@@ -196,12 +250,6 @@
     <t>PORRAS</t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>ROSALES</t>
   </si>
   <si>
@@ -214,16 +262,76 @@
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS DAMIAN</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>IRVING EMILIO</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>MAYRIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
     <t>VICTOR YAEL</t>
   </si>
   <si>
-    <t>MARIA MICHELLE</t>
+    <t>YARETH</t>
   </si>
   <si>
     <t>BETZY AYELEN</t>
   </si>
   <si>
-    <t>EVAN LAEL</t>
+    <t>ERIKA VALERIA</t>
   </si>
   <si>
     <t>ANGEL ISMAEL</t>
@@ -232,64 +340,40 @@
     <t>GABRIEL URYEL</t>
   </si>
   <si>
-    <t>JESUS ENRIQUE</t>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
   </si>
   <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
+    <t>JOSE GABRIEL</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>JHOCELIN VALENTINA</t>
+  </si>
+  <si>
+    <t>KEVIN JESUS</t>
+  </si>
+  <si>
+    <t>EUNICE GUADALUPE</t>
+  </si>
+  <si>
+    <t>HEIDI ABRIL</t>
+  </si>
+  <si>
+    <t>MARTIN ERNESTO</t>
+  </si>
+  <si>
+    <t>SABDIEL JIREH</t>
+  </si>
+  <si>
     <t>ALEYDA MONSERRAT</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>YARETH</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>JHOCELIN VALENTINA</t>
-  </si>
-  <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
-    <t>MARBELY YOSELIN</t>
-  </si>
-  <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>ERIKA VALERIA</t>
-  </si>
-  <si>
-    <t>IRVING JESUS</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>EUNICE GUADALUPE</t>
-  </si>
-  <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
-    <t>SABDIEL JIREH</t>
   </si>
   <si>
     <t>KEVYN DANIEL</t>
@@ -702,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -754,16 +838,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>45.45</v>
+        <v>48.48</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -789,7 +873,7 @@
         <v>47.83</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -958,7 +1042,7 @@
         <v>69.7</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -984,7 +1068,7 @@
         <v>52.17</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1153,7 +1237,7 @@
         <v>69.7</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1179,7 +1263,7 @@
         <v>52.17</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1241,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1273,16 +1357,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920092</v>
+        <v>24330051920101</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1296,22 +1380,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920400</v>
+        <v>24330051920104</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1319,22 +1403,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920194</v>
+        <v>24330051920393</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1342,22 +1426,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920202</v>
+        <v>24330051920260</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1365,22 +1449,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920239</v>
+        <v>23330051920183</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1388,22 +1472,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920267</v>
+        <v>23330051920189</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1411,22 +1495,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920369</v>
+        <v>23330051920195</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1434,22 +1518,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920283</v>
+        <v>23330051920202</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>4</v>
@@ -1457,137 +1541,137 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920312</v>
+        <v>24330051920400</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920183</v>
+        <v>24330051920355</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920189</v>
+        <v>24330051920394</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920195</v>
+        <v>24330051920406</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920202</v>
+        <v>24330051920202</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920098</v>
+        <v>24330051920389</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -1595,22 +1679,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920355</v>
+        <v>24330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1618,22 +1702,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920179</v>
+        <v>24330051920407</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -1641,22 +1725,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920298</v>
+        <v>24330051920409</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -1664,22 +1748,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920330</v>
+        <v>24330051920258</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -1687,16 +1771,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920390</v>
+        <v>24330051920405</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1710,16 +1794,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920262</v>
+        <v>24330051920369</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1733,22 +1817,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920238</v>
+        <v>24330051920092</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1756,22 +1840,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920256</v>
+        <v>24330051920098</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1779,22 +1863,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920203</v>
+        <v>24330051920194</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1802,16 +1886,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920226</v>
+        <v>24330051920238</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1820,121 +1904,397 @@
         <v>12</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920270</v>
+        <v>24330051920239</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920323</v>
+        <v>24330051920267</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920192</v>
+        <v>24330051920256</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920329</v>
+        <v>24330051920390</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
+        <v>24330051920283</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>24330051920293</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>110</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>23330051920203</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>24330051920179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23330051920298</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>24330051920226</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>24330051920262</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>24330051920270</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" t="s">
+        <v>116</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>24330051920323</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>23330051920312</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>23330051920192</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>23330051920329</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
         <v>23330051920201</v>
       </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" t="s">
         <v>9</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F42" t="s">
         <v>15</v>
       </c>
-      <c r="G30">
+      <c r="G42">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="109">
   <si>
     <t>Mat</t>
   </si>
@@ -85,304 +85,265 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZENDEJAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>NIETO</t>
   </si>
   <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
+  </si>
+  <si>
+    <t>RUL</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANIAGUA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>RUL</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
     <t>ERWIN ISRAEL</t>
   </si>
   <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>JESUS DAMIAN</t>
   </si>
   <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>MAYRIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JOSE GABRIEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>VICTOR YAEL</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>HEIDI ABRIL</t>
+  </si>
+  <si>
+    <t>MARTIN ERNESTO</t>
+  </si>
+  <si>
+    <t>ALEYDA MONSERRAT</t>
+  </si>
+  <si>
     <t>FERNANDO</t>
   </si>
   <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>IRVING EMILIO</t>
-  </si>
-  <si>
-    <t>EVAN LAEL</t>
-  </si>
-  <si>
-    <t>MAYRIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>SERGIO ALAN</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>VICTOR YAEL</t>
-  </si>
-  <si>
-    <t>YARETH</t>
-  </si>
-  <si>
-    <t>BETZY AYELEN</t>
-  </si>
-  <si>
-    <t>ERIKA VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL ISMAEL</t>
-  </si>
-  <si>
-    <t>GABRIEL URYEL</t>
-  </si>
-  <si>
-    <t>IRVING JESUS</t>
-  </si>
-  <si>
-    <t>MARBELY YOSELIN</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>JOSE GABRIEL</t>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>JUAN RAMON</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>JHOCELIN VALENTINA</t>
-  </si>
-  <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>EUNICE GUADALUPE</t>
-  </si>
-  <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
-    <t>SABDIEL JIREH</t>
-  </si>
-  <si>
-    <t>ALEYDA MONSERRAT</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1146,7 @@
         <v>82.5</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1202,16 +1163,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>67.65000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1228,16 +1189,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>69.7</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1280,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1325,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1357,16 +1318,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920101</v>
+        <v>24330051920104</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1380,16 +1341,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1403,22 +1364,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920393</v>
+        <v>24330051920394</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1426,22 +1387,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920260</v>
+        <v>24330051920330</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1449,22 +1410,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920183</v>
+        <v>24330051920407</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1472,22 +1433,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920189</v>
+        <v>24330051920260</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1495,68 +1456,68 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920195</v>
+        <v>24330051920213</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920202</v>
+        <v>24330051920389</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920400</v>
+        <v>24330051920239</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1564,22 +1525,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920355</v>
+        <v>24330051920409</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1587,22 +1548,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920394</v>
+        <v>24330051920256</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -1610,22 +1571,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920406</v>
+        <v>24330051920405</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -1633,22 +1594,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920202</v>
+        <v>24330051920390</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -1656,22 +1617,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920389</v>
+        <v>24330051920369</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -1679,22 +1640,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920330</v>
+        <v>24330051920293</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1702,22 +1663,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920407</v>
+        <v>22330051920389</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -1725,22 +1686,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920409</v>
+        <v>23330051920195</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -1748,22 +1709,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920258</v>
+        <v>23330051920332</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -1771,68 +1732,68 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920405</v>
+        <v>24330051920092</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920369</v>
+        <v>24330051920400</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920092</v>
+        <v>24330051920194</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1840,22 +1801,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920098</v>
+        <v>24330051920267</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1863,22 +1824,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920194</v>
+        <v>24330051920258</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1886,22 +1847,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920238</v>
+        <v>24330051920283</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1909,22 +1870,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920239</v>
+        <v>23330051920189</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1932,39 +1893,39 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920267</v>
+        <v>24330051920098</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920256</v>
+        <v>24330051920262</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1973,21 +1934,21 @@
         <v>13</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920390</v>
+        <v>24330051920270</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1996,21 +1957,21 @@
         <v>13</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920283</v>
+        <v>23330051920312</v>
       </c>
       <c r="B30" t="s">
         <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2019,44 +1980,44 @@
         <v>14</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920293</v>
+        <v>23330051920183</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2065,27 +2026,27 @@
         <v>15</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920179</v>
+        <v>23330051920329</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2093,22 +2054,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920298</v>
+        <v>23330051920201</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2116,185 +2077,24 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920226</v>
+        <v>23330051920203</v>
       </c>
       <c r="B35" t="s">
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>24330051920262</v>
-      </c>
-      <c r="B36" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>24330051920270</v>
-      </c>
-      <c r="B37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>24330051920323</v>
-      </c>
-      <c r="B38" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>23330051920312</v>
-      </c>
-      <c r="B39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>23330051920192</v>
-      </c>
-      <c r="B40" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" t="s">
-        <v>119</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>23330051920329</v>
-      </c>
-      <c r="B41" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>23330051920201</v>
-      </c>
-      <c r="B42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" t="s">
-        <v>74</v>
-      </c>
-      <c r="D42" t="s">
-        <v>121</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="95">
   <si>
     <t>Mat</t>
   </si>
@@ -139,9 +139,6 @@
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -154,15 +151,9 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -214,30 +205,15 @@
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>CHACON</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
     <t>BALDERAS</t>
   </si>
   <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -307,40 +283,22 @@
     <t>BETZY AYELEN</t>
   </si>
   <si>
-    <t>GABRIEL URYEL</t>
-  </si>
-  <si>
     <t>SERGIO ALAN</t>
   </si>
   <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
     <t>YARETH</t>
   </si>
   <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
     <t>ALEYDA MONSERRAT</t>
   </si>
   <si>
     <t>FERNANDO</t>
   </si>
   <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
     <t>SABDY</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
@@ -1215,16 +1173,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>52.17</v>
+        <v>65.22</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1267,16 +1225,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>47.62</v>
+        <v>61.9</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1286,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1324,10 +1282,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1347,10 +1305,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1370,10 +1328,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1393,10 +1351,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1419,7 +1377,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1439,10 +1397,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1462,10 +1420,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1485,10 +1443,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1508,10 +1466,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1531,10 +1489,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1554,10 +1512,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1577,10 +1535,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1603,7 +1561,7 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1626,7 +1584,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1646,10 +1604,10 @@
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1669,10 +1627,10 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1692,10 +1650,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1715,10 +1673,10 @@
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1738,10 +1696,10 @@
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1761,10 +1719,10 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1784,10 +1742,10 @@
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1801,16 +1759,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920267</v>
+        <v>24330051920258</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1824,22 +1782,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920258</v>
+        <v>24330051920283</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1847,68 +1805,68 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920283</v>
+        <v>24330051920098</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920189</v>
+        <v>23330051920312</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920098</v>
+        <v>23330051920183</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1916,22 +1874,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920262</v>
+        <v>23330051920329</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1939,162 +1897,24 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920270</v>
+        <v>23330051920203</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920312</v>
-      </c>
-      <c r="B30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920183</v>
-      </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>23330051920192</v>
-      </c>
-      <c r="B32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>23330051920329</v>
-      </c>
-      <c r="B33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23330051920201</v>
-      </c>
-      <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>23330051920203</v>
-      </c>
-      <c r="B35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20241.xlsx
@@ -85,24 +85,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
@@ -124,6 +124,15 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -133,21 +142,12 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>CHICO</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -187,6 +187,18 @@
     <t>RUL</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>LAGUNA</t>
   </si>
   <si>
@@ -196,18 +208,6 @@
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>BALDERAS</t>
   </si>
   <si>
@@ -220,24 +220,24 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS DAMIAN</t>
+  </si>
+  <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
-    <t>ERWIN ISRAEL</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS DAMIAN</t>
-  </si>
-  <si>
     <t>SANDY CAMILA</t>
   </si>
   <si>
@@ -265,6 +265,18 @@
     <t>JOSE GABRIEL</t>
   </si>
   <si>
+    <t>VICTOR YAEL</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
@@ -274,22 +286,10 @@
     <t>SERGIO JOSUE</t>
   </si>
   <si>
-    <t>VICTOR YAEL</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>BETZY AYELEN</t>
-  </si>
-  <si>
-    <t>SERGIO ALAN</t>
+    <t>YARETH</t>
   </si>
   <si>
     <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>YARETH</t>
   </si>
   <si>
     <t>ALEYDA MONSERRAT</t>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
         <v>67</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920393</v>
+        <v>24330051920394</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>68</v>
@@ -1314,7 +1314,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920394</v>
+        <v>24330051920330</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
         <v>69</v>
@@ -1337,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920330</v>
+        <v>24330051920407</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
         <v>70</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920407</v>
+        <v>24330051920260</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
         <v>71</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920260</v>
+        <v>24330051920104</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>
@@ -1406,10 +1406,10 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1486,7 +1486,7 @@
         <v>24330051920409</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -1555,10 +1555,10 @@
         <v>24330051920390</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -1581,7 +1581,7 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -1621,7 +1621,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920389</v>
+        <v>24330051920092</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
@@ -1633,18 +1633,18 @@
         <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920195</v>
+        <v>24330051920400</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -1656,21 +1656,21 @@
         <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920332</v>
+        <v>24330051920194</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>58</v>
@@ -1679,21 +1679,21 @@
         <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920092</v>
+        <v>24330051920258</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
         <v>59</v>
@@ -1705,7 +1705,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920400</v>
+        <v>22330051920389</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
         <v>60</v>
@@ -1725,10 +1725,10 @@
         <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920194</v>
+        <v>23330051920195</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
         <v>61</v>
@@ -1748,10 +1748,10 @@
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920258</v>
+        <v>23330051920332</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
@@ -1771,10 +1771,10 @@
         <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1782,13 +1782,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920283</v>
+        <v>24330051920098</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
         <v>89</v>
@@ -1797,21 +1797,21 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920098</v>
+        <v>24330051920283</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
         <v>90</v>
@@ -1820,7 +1820,7 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         <v>23330051920183</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
         <v>64</v>
